--- a/data/GIFI_Master_Mapping_v2.xlsx
+++ b/data/GIFI_Master_Mapping_v2.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GIFI Master Mapping" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fallback - Map No (blank GIFI)" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation Log" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="GIFI Master Mapping" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Fallback - Map No (blank GIFI)" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Validation Log" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'GIFI Master Mapping'!$A$1:$C$58</definedName>
@@ -1453,7 +1453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1655,6 +1655,28 @@
       <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Miscellaneous</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>San_San</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>40. 3</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Administrative</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Insurance</t>
         </is>
       </c>
     </row>

--- a/data/GIFI_Master_Mapping_v2.xlsx
+++ b/data/GIFI_Master_Mapping_v2.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C58"/>
+  <dimension ref="A1:C59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1438,6 +1438,23 @@
       <c r="C58" s="2" t="inlineStr">
         <is>
           <t>Current income tax expense</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>8211</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Gain on Sale</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Res_Her FY2026: one-time $300,000 gain on sale of property, kept separate from Other Operating per user decision (2026-09-22)</t>
         </is>
       </c>
     </row>
